--- a/sources/yoshimitsu_step6b.xlsx
+++ b/sources/yoshimitsu_step6b.xlsx
@@ -430,7 +430,7 @@
     <col width="21" customWidth="1" min="8" max="8"/>
     <col width="24" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
@@ -4832,7 +4832,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="Q83" t="inlineStr">
@@ -6032,7 +6032,7 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="Q106" t="inlineStr">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="Q107" t="inlineStr">
@@ -6151,7 +6151,7 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="Q108" t="inlineStr">
@@ -6478,7 +6478,7 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>!![!]</t>
+          <t>!!!</t>
         </is>
       </c>
       <c r="Q114" t="inlineStr">
@@ -6535,7 +6535,7 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>m[!]</t>
+          <t>m!</t>
         </is>
       </c>
       <c r="Q115" t="inlineStr">
@@ -6951,7 +6951,7 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="Q123" t="inlineStr">
@@ -7030,7 +7030,7 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="O125" t="inlineStr">
@@ -7092,7 +7092,7 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="Q126" t="inlineStr">
@@ -7144,7 +7144,7 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="Q127" t="inlineStr">
@@ -7201,7 +7201,7 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="Q128" t="inlineStr">
@@ -7467,7 +7467,7 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>hmmhhLm[!][!]!</t>
+          <t>hmmhhLm!!!</t>
         </is>
       </c>
       <c r="R134" t="inlineStr">
@@ -7499,7 +7499,7 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>hmmhmmmm[!]!</t>
+          <t>hmmhmmmm!!</t>
         </is>
       </c>
       <c r="R135" t="inlineStr">
@@ -7531,7 +7531,7 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>hhmhhLm[!][!]!</t>
+          <t>hhmhhLm!!!</t>
         </is>
       </c>
       <c r="R136" t="inlineStr">

--- a/sources/yoshimitsu_step6b.xlsx
+++ b/sources/yoshimitsu_step6b.xlsx
@@ -728,6 +728,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>354a3fa8-57b9-4015-af73-fbbd2a144a43</t>
+        </is>
+      </c>
       <c r="R6" t="inlineStr">
         <is>
           <t>354a3fa8-57b9-4015-af73-fbbd2a144a43</t>
@@ -775,6 +780,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>20aa9f1d-6b31-434f-844f-26957fc46e7e</t>
+        </is>
+      </c>
       <c r="R7" t="inlineStr">
         <is>
           <t>20aa9f1d-6b31-434f-844f-26957fc46e7e</t>
@@ -820,6 +830,11 @@
       <c r="M8" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>7e99b815-adc2-430a-a808-4fc52a37e967</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -7470,6 +7485,11 @@
           <t>hmmhhLm!!!</t>
         </is>
       </c>
+      <c r="Q134" t="inlineStr">
+        <is>
+          <t>7a24210e-7ae9-446c-a303-2ad7eba2ac12</t>
+        </is>
+      </c>
       <c r="R134" t="inlineStr">
         <is>
           <t>7a24210e-7ae9-446c-a303-2ad7eba2ac12</t>
@@ -7502,6 +7522,11 @@
           <t>hmmhmmmm!!</t>
         </is>
       </c>
+      <c r="Q135" t="inlineStr">
+        <is>
+          <t>e7491c61-b40c-4c01-87b6-9b84db2d350e</t>
+        </is>
+      </c>
       <c r="R135" t="inlineStr">
         <is>
           <t>e7491c61-b40c-4c01-87b6-9b84db2d350e</t>
@@ -7534,6 +7559,11 @@
           <t>hhmhhLm!!!</t>
         </is>
       </c>
+      <c r="Q136" t="inlineStr">
+        <is>
+          <t>51b32f66-b200-49c0-ad4b-c52c71e51bcd</t>
+        </is>
+      </c>
       <c r="R136" t="inlineStr">
         <is>
           <t>51b32f66-b200-49c0-ad4b-c52c71e51bcd</t>
@@ -7566,6 +7596,11 @@
           <t>hmmhhLmm</t>
         </is>
       </c>
+      <c r="Q137" t="inlineStr">
+        <is>
+          <t>11bf5f22-1ce6-4a60-a66b-d9ef064953bb</t>
+        </is>
+      </c>
       <c r="R137" t="inlineStr">
         <is>
           <t>11bf5f22-1ce6-4a60-a66b-d9ef064953bb</t>
@@ -7598,6 +7633,11 @@
           <t>hhmhhLmm</t>
         </is>
       </c>
+      <c r="Q138" t="inlineStr">
+        <is>
+          <t>9b6d5b1e-d48e-46f1-b1c7-21d5b7e3d2e1</t>
+        </is>
+      </c>
       <c r="R138" t="inlineStr">
         <is>
           <t>9b6d5b1e-d48e-46f1-b1c7-21d5b7e3d2e1</t>
@@ -7630,6 +7670,11 @@
           <t>hhmh!</t>
         </is>
       </c>
+      <c r="Q139" t="inlineStr">
+        <is>
+          <t>1d6b4525-e2f5-45b8-b095-3e41e4cec56b</t>
+        </is>
+      </c>
       <c r="R139" t="inlineStr">
         <is>
           <t>1d6b4525-e2f5-45b8-b095-3e41e4cec56b</t>
@@ -7660,6 +7705,11 @@
       <c r="K140" t="inlineStr">
         <is>
           <t>hhmh!</t>
+        </is>
+      </c>
+      <c r="Q140" t="inlineStr">
+        <is>
+          <t>d39521f6-f2ff-4975-8663-4aac08ebeffc</t>
         </is>
       </c>
       <c r="R140" t="inlineStr">

--- a/sources/yoshimitsu_step6b.xlsx
+++ b/sources/yoshimitsu_step6b.xlsx
@@ -2907,6 +2907,11 @@
           <t>– 1+4</t>
         </is>
       </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2+3</t>
+        </is>
+      </c>
       <c r="C49" t="inlineStr">
         <is>
           <t>– Soul Siphon</t>
@@ -2959,6 +2964,11 @@
           <t>– F+1+4</t>
         </is>
       </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>F+2+3</t>
+        </is>
+      </c>
       <c r="C50" t="inlineStr">
         <is>
           <t>– Possession</t>
@@ -4166,6 +4176,11 @@
           <t>– f</t>
         </is>
       </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
       <c r="C71" t="inlineStr">
         <is>
           <t>– Vacuum Dance</t>
@@ -4431,6 +4446,11 @@
           <t>– 1+4</t>
         </is>
       </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2+3</t>
+        </is>
+      </c>
       <c r="C76" t="inlineStr">
         <is>
           <t>– Soul Siphon</t>
@@ -4483,6 +4503,11 @@
           <t>– F+1+4</t>
         </is>
       </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>F+2+3</t>
+        </is>
+      </c>
       <c r="C77" t="inlineStr">
         <is>
           <t>– Possession</t>
@@ -4949,6 +4974,11 @@
       <c r="A86" t="inlineStr">
         <is>
           <t>– f</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>b</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -6067,6 +6097,11 @@
           <t>– ub</t>
         </is>
       </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>u; uf</t>
+        </is>
+      </c>
       <c r="C107" t="inlineStr">
         <is>
           <t>– Jumping Flea</t>
@@ -6127,6 +6162,11 @@
       <c r="A108" t="inlineStr">
         <is>
           <t>– f,f</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>b,b</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
